--- a/outputs/validation/comparison_manual_model_41.xlsx
+++ b/outputs/validation/comparison_manual_model_41.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,38 +684,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>051</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0175</v>
+        <v>0.007</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J6" t="n">
         <v>0.872</v>
       </c>
       <c r="K6" t="n">
-        <v>0.889</v>
+        <v>0.912</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.912</v>
       </c>
       <c r="M6" t="n">
-        <v>0.914</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="7">
@@ -731,38 +731,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="F7" t="n">
-        <v>0.55</v>
+        <v>0.42</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0042</v>
+        <v>0.0175</v>
       </c>
       <c r="H7" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>0.766</v>
+        <v>0.872</v>
       </c>
       <c r="K7" t="n">
-        <v>0.926</v>
+        <v>0.889</v>
       </c>
       <c r="L7" t="n">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.82</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="8">
@@ -778,38 +778,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006</v>
+        <v>0.0042</v>
       </c>
       <c r="H8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I8" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>0.872</v>
+        <v>0.766</v>
       </c>
       <c r="K8" t="n">
-        <v>0.889</v>
+        <v>0.926</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="M8" t="n">
-        <v>0.914</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -872,38 +872,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="F10" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0042</v>
+        <v>0.006</v>
       </c>
       <c r="H10" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J10" t="n">
-        <v>0.745</v>
+        <v>0.872</v>
       </c>
       <c r="K10" t="n">
-        <v>0.893</v>
+        <v>0.889</v>
       </c>
       <c r="L10" t="n">
-        <v>0.735</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.806</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="11">
@@ -919,38 +919,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0021</v>
+        <v>0.0042</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.83</v>
+        <v>0.745</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="L11" t="n">
-        <v>0.824</v>
+        <v>0.735</v>
       </c>
       <c r="M11" t="n">
-        <v>0.875</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="12">
@@ -966,38 +966,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0154</v>
+        <v>0.0021</v>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>0.915</v>
+        <v>0.83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.917</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>0.971</v>
+        <v>0.824</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="13">
@@ -1013,38 +1013,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="E13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.42</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.37</v>
-      </c>
       <c r="G13" t="n">
-        <v>0.0537</v>
+        <v>0.0154</v>
       </c>
       <c r="H13" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.915</v>
       </c>
       <c r="K13" t="n">
-        <v>0.903</v>
+        <v>0.917</v>
       </c>
       <c r="L13" t="n">
-        <v>0.824</v>
+        <v>0.971</v>
       </c>
       <c r="M13" t="n">
-        <v>0.862</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1060,38 +1060,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="F14" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0051</v>
+        <v>0.0537</v>
       </c>
       <c r="H14" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I14" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>0.915</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.917</v>
+        <v>0.903</v>
       </c>
       <c r="L14" t="n">
-        <v>0.971</v>
+        <v>0.824</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="15">
@@ -1107,38 +1107,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0113</v>
+        <v>0.0051</v>
       </c>
       <c r="H15" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.915</v>
       </c>
       <c r="K15" t="n">
-        <v>0.903</v>
+        <v>0.917</v>
       </c>
       <c r="L15" t="n">
-        <v>0.824</v>
+        <v>0.971</v>
       </c>
       <c r="M15" t="n">
-        <v>0.862</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1154,38 +1154,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006</v>
+        <v>0.0113</v>
       </c>
       <c r="H16" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J16" t="n">
-        <v>0.872</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.889</v>
+        <v>0.903</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="M16" t="n">
-        <v>0.914</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="17">
@@ -1201,38 +1201,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="F17" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0175</v>
+        <v>0.006</v>
       </c>
       <c r="H17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I17" t="n">
         <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>0.851</v>
+        <v>0.872</v>
       </c>
       <c r="K17" t="n">
-        <v>0.865</v>
+        <v>0.889</v>
       </c>
       <c r="L17" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.901</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="18">
@@ -1248,38 +1248,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="F18" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0433</v>
+        <v>0.0175</v>
       </c>
       <c r="H18" t="n">
+        <v>37</v>
+      </c>
+      <c r="I18" t="n">
         <v>32</v>
       </c>
-      <c r="I18" t="n">
-        <v>30</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.872</v>
+        <v>0.851</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="L18" t="n">
-        <v>0.882</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.909</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="19">
@@ -1295,38 +1295,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009</v>
+        <v>0.0433</v>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
         <v>0.872</v>
       </c>
       <c r="K19" t="n">
-        <v>0.889</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="M19" t="n">
-        <v>0.914</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="20">
@@ -1342,38 +1342,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0524</v>
+        <v>0.0009</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" t="n">
-        <v>0.894</v>
+        <v>0.872</v>
       </c>
       <c r="K20" t="n">
-        <v>0.892</v>
+        <v>0.889</v>
       </c>
       <c r="L20" t="n">
-        <v>0.971</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.93</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="21">
@@ -1389,38 +1389,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.34</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.42</v>
-      </c>
       <c r="G21" t="n">
-        <v>0.0136</v>
+        <v>0.0524</v>
       </c>
       <c r="H21" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J21" t="n">
-        <v>0.723</v>
+        <v>0.894</v>
       </c>
       <c r="K21" t="n">
-        <v>0.723</v>
+        <v>0.892</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="M21" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="22">
@@ -1436,38 +1436,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="E22" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="F22" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0315</v>
+        <v>0.0136</v>
       </c>
       <c r="H22" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="I22" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J22" t="n">
-        <v>0.851</v>
+        <v>0.723</v>
       </c>
       <c r="K22" t="n">
-        <v>0.846</v>
+        <v>0.723</v>
       </c>
       <c r="L22" t="n">
-        <v>0.971</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0.904</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="23">
@@ -1483,38 +1483,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="F23" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0044</v>
+        <v>0.0315</v>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J23" t="n">
-        <v>0.723</v>
+        <v>0.851</v>
       </c>
       <c r="K23" t="n">
-        <v>0.723</v>
+        <v>0.846</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.971</v>
       </c>
       <c r="M23" t="n">
-        <v>0.84</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="24">
@@ -1530,38 +1530,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="E24" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0175</v>
+        <v>0.0044</v>
       </c>
       <c r="H24" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="I24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J24" t="n">
-        <v>0.83</v>
+        <v>0.723</v>
       </c>
       <c r="K24" t="n">
-        <v>0.842</v>
+        <v>0.723</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9409999999999999</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0.889</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="25">
@@ -1577,44 +1577,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="E25" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0007</v>
+        <v>0.0175</v>
       </c>
       <c r="H25" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>0.851</v>
+        <v>0.83</v>
       </c>
       <c r="K25" t="n">
-        <v>0.846</v>
+        <v>0.842</v>
       </c>
       <c r="L25" t="n">
-        <v>0.971</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>0.904</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ideology_manual_vs_all_models</t>
+          <t>video_type_vs_all_models</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1624,38 +1624,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E26" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.0007</v>
       </c>
       <c r="H26" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J26" t="n">
-        <v>0.745</v>
+        <v>0.851</v>
       </c>
       <c r="K26" t="n">
-        <v>0.923</v>
+        <v>0.846</v>
       </c>
       <c r="L26" t="n">
-        <v>0.706</v>
+        <v>0.971</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="27">
@@ -1671,38 +1671,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I27" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>0.872</v>
+        <v>0.745</v>
       </c>
       <c r="K27" t="n">
-        <v>0.912</v>
+        <v>0.923</v>
       </c>
       <c r="L27" t="n">
-        <v>0.912</v>
+        <v>0.706</v>
       </c>
       <c r="M27" t="n">
-        <v>0.912</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28">
@@ -1718,38 +1718,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1.02</v>
+        <v>0.78</v>
       </c>
       <c r="E28" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="F28" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J28" t="n">
-        <v>0.787</v>
+        <v>0.872</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9</v>
+        <v>0.912</v>
       </c>
       <c r="L28" t="n">
-        <v>0.794</v>
+        <v>0.912</v>
       </c>
       <c r="M28" t="n">
-        <v>0.844</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="29">
@@ -1765,38 +1765,38 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="E29" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I29" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>0.872</v>
+        <v>0.787</v>
       </c>
       <c r="K29" t="n">
-        <v>0.889</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="M29" t="n">
-        <v>0.914</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="30">
@@ -1812,38 +1812,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>051</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="E30" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="F30" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>0.745</v>
+        <v>0.872</v>
       </c>
       <c r="K30" t="n">
-        <v>0.893</v>
+        <v>0.912</v>
       </c>
       <c r="L30" t="n">
-        <v>0.735</v>
+        <v>0.912</v>
       </c>
       <c r="M30" t="n">
-        <v>0.806</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="31">
@@ -1859,17 +1859,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="F31" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1878,19 +1878,19 @@
         <v>36</v>
       </c>
       <c r="I31" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="n">
-        <v>0.915</v>
+        <v>0.872</v>
       </c>
       <c r="K31" t="n">
-        <v>0.917</v>
+        <v>0.889</v>
       </c>
       <c r="L31" t="n">
-        <v>0.971</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="32">
@@ -1906,38 +1906,38 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="F32" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="K32" t="n">
-        <v>0.903</v>
+        <v>0.893</v>
       </c>
       <c r="L32" t="n">
-        <v>0.824</v>
+        <v>0.735</v>
       </c>
       <c r="M32" t="n">
-        <v>0.862</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="33">
@@ -1953,17 +1953,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="E33" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1972,25 +1972,25 @@
         <v>36</v>
       </c>
       <c r="I33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J33" t="n">
-        <v>0.872</v>
+        <v>0.915</v>
       </c>
       <c r="K33" t="n">
-        <v>0.889</v>
+        <v>0.917</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="M33" t="n">
-        <v>0.914</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ideology_all_statements_vs_all_models</t>
+          <t>ideology_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="F34" t="n">
         <v>0.86</v>
@@ -2016,28 +2016,28 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>0.787</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9</v>
+        <v>0.903</v>
       </c>
       <c r="L34" t="n">
-        <v>0.794</v>
+        <v>0.824</v>
       </c>
       <c r="M34" t="n">
-        <v>0.844</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ideology_all_statements_vs_all_models</t>
+          <t>ideology_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2047,17 +2047,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="E35" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="F35" t="n">
-        <v>0.92</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2094,38 +2094,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" t="n">
         <v>27</v>
       </c>
-      <c r="I36" t="n">
-        <v>25</v>
-      </c>
       <c r="J36" t="n">
-        <v>0.766</v>
+        <v>0.787</v>
       </c>
       <c r="K36" t="n">
-        <v>0.926</v>
+        <v>0.9</v>
       </c>
       <c r="L36" t="n">
-        <v>0.735</v>
+        <v>0.794</v>
       </c>
       <c r="M36" t="n">
-        <v>0.82</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="37">
@@ -2141,38 +2141,38 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>051</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="E37" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="F37" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I37" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
         <v>0.872</v>
       </c>
       <c r="K37" t="n">
-        <v>0.889</v>
+        <v>0.912</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.912</v>
       </c>
       <c r="M37" t="n">
-        <v>0.914</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="38">
@@ -2188,38 +2188,38 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="E38" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="F38" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J38" t="n">
-        <v>0.83</v>
+        <v>0.872</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.889</v>
       </c>
       <c r="L38" t="n">
-        <v>0.824</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>0.875</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="39">
@@ -2235,38 +2235,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>06</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
       <c r="E39" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="F39" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="I39" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>0.915</v>
+        <v>0.766</v>
       </c>
       <c r="K39" t="n">
-        <v>0.917</v>
+        <v>0.926</v>
       </c>
       <c r="L39" t="n">
-        <v>0.971</v>
+        <v>0.735</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="40">
@@ -2282,14 +2282,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="F40" t="n">
         <v>0.88</v>
@@ -2298,22 +2298,22 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.872</v>
       </c>
       <c r="K40" t="n">
-        <v>0.903</v>
+        <v>0.889</v>
       </c>
       <c r="L40" t="n">
-        <v>0.824</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>0.862</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="41">
@@ -2329,44 +2329,44 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="E41" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="F41" t="n">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I41" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>0.851</v>
+        <v>0.83</v>
       </c>
       <c r="K41" t="n">
-        <v>0.865</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="M41" t="n">
-        <v>0.901</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>populism_manual_vs_all_models</t>
+          <t>ideology_all_statements_vs_all_models</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2376,44 +2376,44 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="E42" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="F42" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J42" t="n">
-        <v>0.745</v>
+        <v>0.915</v>
       </c>
       <c r="K42" t="n">
-        <v>0.923</v>
+        <v>0.917</v>
       </c>
       <c r="L42" t="n">
-        <v>0.706</v>
+        <v>0.971</v>
       </c>
       <c r="M42" t="n">
-        <v>0.8</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>populism_manual_vs_all_models</t>
+          <t>ideology_all_statements_vs_all_models</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2423,44 +2423,44 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.05</v>
+        <v>0.84</v>
       </c>
       <c r="E43" t="n">
-        <v>2.27</v>
+        <v>1.24</v>
       </c>
       <c r="F43" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J43" t="n">
-        <v>0.872</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.912</v>
+        <v>0.903</v>
       </c>
       <c r="L43" t="n">
-        <v>0.912</v>
+        <v>0.824</v>
       </c>
       <c r="M43" t="n">
-        <v>0.912</v>
+        <v>0.862</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>populism_manual_vs_all_models</t>
+          <t>ideology_all_statements_vs_all_models</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2470,38 +2470,38 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.11</v>
+        <v>0.77</v>
       </c>
       <c r="E44" t="n">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="F44" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>0.787</v>
+        <v>0.851</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9</v>
+        <v>0.865</v>
       </c>
       <c r="L44" t="n">
-        <v>0.794</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>0.844</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="45">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>26</v>
+      </c>
+      <c r="I45" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="M45" t="n">
         <v>0.8</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>36</v>
-      </c>
-      <c r="I45" t="n">
-        <v>32</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.872</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.914</v>
       </c>
     </row>
     <row r="46">
@@ -2564,38 +2564,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>03</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.58</v>
+        <v>1.05</v>
       </c>
       <c r="E46" t="n">
-        <v>2.76</v>
+        <v>2.27</v>
       </c>
       <c r="F46" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I46" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J46" t="n">
         <v>0.872</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.912</v>
       </c>
       <c r="L46" t="n">
-        <v>0.882</v>
+        <v>0.912</v>
       </c>
       <c r="M46" t="n">
-        <v>0.909</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="47">
@@ -2611,38 +2611,38 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>04</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="E47" t="n">
-        <v>2.79</v>
+        <v>1.9</v>
       </c>
       <c r="F47" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I47" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>0.894</v>
+        <v>0.787</v>
       </c>
       <c r="K47" t="n">
-        <v>0.892</v>
+        <v>0.9</v>
       </c>
       <c r="L47" t="n">
-        <v>0.971</v>
+        <v>0.794</v>
       </c>
       <c r="M47" t="n">
-        <v>0.93</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="48">
@@ -2658,38 +2658,38 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>051</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="E48" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="F48" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I48" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J48" t="n">
-        <v>0.723</v>
+        <v>0.872</v>
       </c>
       <c r="K48" t="n">
-        <v>0.723</v>
+        <v>0.912</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0.912</v>
       </c>
       <c r="M48" t="n">
-        <v>0.84</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="49">
@@ -2705,44 +2705,44 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>07</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.19</v>
+        <v>0.8</v>
       </c>
       <c r="E49" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="F49" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I49" t="n">
         <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>0.83</v>
+        <v>0.872</v>
       </c>
       <c r="K49" t="n">
-        <v>0.842</v>
+        <v>0.889</v>
       </c>
       <c r="L49" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>0.889</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>populism_all_statements_vs_all_models</t>
+          <t>populism_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2752,44 +2752,44 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="E50" t="n">
-        <v>2.43</v>
+        <v>2.76</v>
       </c>
       <c r="F50" t="n">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
+        <v>32</v>
+      </c>
+      <c r="I50" t="n">
         <v>30</v>
       </c>
-      <c r="I50" t="n">
-        <v>27</v>
-      </c>
       <c r="J50" t="n">
-        <v>0.787</v>
+        <v>0.872</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>0.794</v>
+        <v>0.882</v>
       </c>
       <c r="M50" t="n">
-        <v>0.844</v>
+        <v>0.909</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>populism_all_statements_vs_all_models</t>
+          <t>populism_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2799,44 +2799,44 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.09</v>
+        <v>1.52</v>
       </c>
       <c r="E51" t="n">
-        <v>1.88</v>
+        <v>2.79</v>
       </c>
       <c r="F51" t="n">
-        <v>0.92</v>
+        <v>0.77</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J51" t="n">
-        <v>0.872</v>
+        <v>0.894</v>
       </c>
       <c r="K51" t="n">
-        <v>0.889</v>
+        <v>0.892</v>
       </c>
       <c r="L51" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.971</v>
       </c>
       <c r="M51" t="n">
-        <v>0.914</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>populism_all_statements_vs_all_models</t>
+          <t>populism_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2846,44 +2846,44 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>47</v>
+      </c>
+      <c r="I52" t="n">
+        <v>34</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
         <v>0.84</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>27</v>
-      </c>
-      <c r="I52" t="n">
-        <v>25</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>populism_all_statements_vs_all_models</t>
+          <t>populism_manual_vs_all_models</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2893,38 +2893,38 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="E53" t="n">
-        <v>1.33</v>
+        <v>2.17</v>
       </c>
       <c r="F53" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I53" t="n">
         <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>0.872</v>
+        <v>0.83</v>
       </c>
       <c r="K53" t="n">
-        <v>0.889</v>
+        <v>0.842</v>
       </c>
       <c r="L53" t="n">
         <v>0.9409999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>0.914</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="54">
@@ -2940,38 +2940,38 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="E54" t="n">
-        <v>2.82</v>
+        <v>2.43</v>
       </c>
       <c r="F54" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I54" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>0.872</v>
+        <v>0.787</v>
       </c>
       <c r="K54" t="n">
-        <v>0.889</v>
+        <v>0.9</v>
       </c>
       <c r="L54" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.794</v>
       </c>
       <c r="M54" t="n">
-        <v>0.914</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="55">
@@ -2987,38 +2987,38 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>051</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.48</v>
+        <v>0.92</v>
       </c>
       <c r="E55" t="n">
-        <v>2.53</v>
+        <v>1.69</v>
       </c>
       <c r="F55" t="n">
-        <v>0.85</v>
+        <v>0.91</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I55" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>0.851</v>
+        <v>0.872</v>
       </c>
       <c r="K55" t="n">
-        <v>0.846</v>
+        <v>0.912</v>
       </c>
       <c r="L55" t="n">
-        <v>0.971</v>
+        <v>0.912</v>
       </c>
       <c r="M55" t="n">
-        <v>0.904</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="56">
@@ -3034,38 +3034,38 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>05</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="E56" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I56" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>0.723</v>
+        <v>0.872</v>
       </c>
       <c r="K56" t="n">
-        <v>0.723</v>
+        <v>0.889</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>0.84</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="57">
@@ -3081,37 +3081,272 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>27</v>
+      </c>
+      <c r="I57" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>populism_all_statements_vs_all_models</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>36</v>
+      </c>
+      <c r="I58" t="n">
+        <v>32</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>populism_all_statements_vs_all_models</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>36</v>
+      </c>
+      <c r="I59" t="n">
+        <v>32</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>populism_all_statements_vs_all_models</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>39</v>
+      </c>
+      <c r="I60" t="n">
+        <v>33</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>populism_all_statements_vs_all_models</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>47</v>
+      </c>
+      <c r="I61" t="n">
+        <v>34</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>populism_all_statements_vs_all_models</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>gemini-2.5-flash</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D62" t="n">
         <v>0.98</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E62" t="n">
         <v>1.53</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F62" t="n">
         <v>0.89</v>
       </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>39</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I62" t="n">
         <v>33</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J62" t="n">
         <v>0.851</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K62" t="n">
         <v>0.846</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L62" t="n">
         <v>0.971</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M62" t="n">
         <v>0.904</v>
       </c>
     </row>
